--- a/AAII_Financials/Quarterly/ACDC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ACDC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>ACDC</t>
   </si>
@@ -656,337 +656,350 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>498100</v>
+      </c>
+      <c r="E8" s="3">
         <v>449600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>436500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>403100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>501900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>600300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>454700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>575300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>579400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>581500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>489100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>574200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>709200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>857500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>794000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>696700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>589800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>345000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>248100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>520300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>135200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>412500</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>388100</v>
+      </c>
+      <c r="E9" s="3">
         <v>354400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>336400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>324100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>374700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>419400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>337600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>390700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>393100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>373700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>334700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>376800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>474600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>545900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>477400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>392000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>339200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>236500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>180900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>389200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>105900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>326700</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E10" s="3">
         <v>95200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>79000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>127200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>180900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>117100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>184600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>186300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>207800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>154400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>197400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>234600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>311600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>316600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>304700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>250600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>108500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>67200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>131100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>29300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>85800</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1013,8 +1026,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1087,8 +1101,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1161,68 +1178,71 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>59400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>9300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>78000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>81200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>49100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>12900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>21300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>500</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1235,82 +1255,88 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E15" s="3">
         <v>97100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>102600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>103000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>104700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>106000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>113300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>112700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>103400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>112800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>107700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>111500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>108900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>110300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>90300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>137900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>128400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>89200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>34700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>106000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>36900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>113800</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,156 +1360,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>528900</v>
+      </c>
+      <c r="E17" s="3">
         <v>495400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>482100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>471200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>550600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>579200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>498900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>568600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>550600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>537300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>490000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>541000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>647000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>734200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>680500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>532200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>506100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>323300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>236700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>550200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>163100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>479600</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-45800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-45600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-68100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-48700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>21100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-44200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>44200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>33200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>62200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>123300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>113500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>164500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>83700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>21700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-29900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-27900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-67100</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1510,218 +1543,225 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-16000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>9400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-18900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-18100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E21" s="3">
         <v>51300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>57400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>35600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>46300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>131900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>70900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>119300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>131700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>158800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>122800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>139800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>163400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>224200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>212000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>232200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>148800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>74100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>46900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>56800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>28600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E22" s="3">
         <v>32800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>33300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>34500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>35100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>35900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>38800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>40600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>39600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>37600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>38800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>40200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>41000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>34900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>16300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>13500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>6700</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -1732,156 +1772,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-71100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-79200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-137900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-112600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-102800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-15100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-83800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-45000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-89300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-104900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-24600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>66500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>101200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>147200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>71300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>20600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-48800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-32800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-85100</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-20200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>17900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-23700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-8400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-6700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>600</v>
-      </c>
-      <c r="U24" s="3">
-        <v>-100</v>
       </c>
       <c r="V24" s="3">
         <v>-100</v>
       </c>
       <c r="W24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,156 +2003,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-74700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-80800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-140500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-92400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-107200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-15400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-101700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-43500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-65600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-96500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-17900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>59800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>105100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>139300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>67400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>20000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-48700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-33000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-85500</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-84900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-144000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-102200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-109300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-18800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-106200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-46400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-67900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-99100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-27500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>22000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>40000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>44000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6600</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>48500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-48500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-31900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-85500</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2176,8 +2234,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2250,8 +2311,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,8 +2388,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2398,156 +2465,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>16000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>18900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>18100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-79700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-83500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-142600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-100900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-108000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-105000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-45200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-66700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-97900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>22000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>40000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>44000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6600</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>48500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-48500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-31900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-85500</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2620,161 +2696,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-79700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-83500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-142600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-100900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-108000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-105000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-45200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-66700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-97900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>22000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>40000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>44000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6600</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>48500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-48500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-31900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-85500</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2801,8 +2886,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2829,71 +2915,72 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E41" s="3">
         <v>33500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>22900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>58000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>25500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>28300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>25300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>25100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>26900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>69900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>64700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>73700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>28700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>16400</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2903,8 +2990,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2977,71 +3067,74 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>339700</v>
+      </c>
+      <c r="E43" s="3">
         <v>324400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>286700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>288200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>352700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>423400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>328800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>371000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>390400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>393700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>352900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>338800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>466200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>597500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>537600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>505800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>448600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>302300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>166100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>104000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3051,71 +3144,74 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>174800</v>
+      </c>
+      <c r="E44" s="3">
         <v>159300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>151300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>166700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>180900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>200100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>201100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>239000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>258800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>219800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>236600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>271900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>304800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>283100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>249500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>238800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>192400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>139100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>73900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>72300</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3125,8 +3221,11 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3169,27 +3268,27 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>43200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>21100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>18700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>9200</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,71 +3298,74 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>572100</v>
+      </c>
+      <c r="E46" s="3">
         <v>534400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>483500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>541300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>580300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>669800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>574100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>680000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>703900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>664600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>638100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>678600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>828900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>993600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>865400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>836200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>735800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>488800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>251700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>201800</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3273,8 +3375,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3296,47 +3401,47 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
-        <v>7500</v>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>7500</v>
       </c>
       <c r="L47" s="3">
+        <v>7500</v>
+      </c>
+      <c r="M47" s="3">
         <v>30400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>28900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>42800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>48400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>53000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>58600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>56800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>49800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>78300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4200</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
+      <c r="W47" s="3">
+        <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
@@ -3347,71 +3452,74 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1479000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1553600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1618600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1699700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1774000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1865500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1919800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1952400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1969900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1767500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1866200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1939500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2013600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2019300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1509300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>899800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>744900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>698800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>363700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>340900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3421,71 +3529,74 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>384000</v>
+      </c>
+      <c r="E49" s="3">
         <v>393000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>402000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>422100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>431200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>440900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>450900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>460200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>461200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>507000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>499400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>505500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>512500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>527700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>443600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>132500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>110600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>28700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>27800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>25600</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3495,8 +3606,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3569,8 +3683,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3643,71 +3760,74 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E52" s="3">
         <v>42000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>40000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>48900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>45200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>44700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>43300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>37400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>37800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>55700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>47400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>46300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>56700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>54100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>22600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>19300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10500</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,8 +3837,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,71 +3914,74 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2507900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2550600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2573100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2742400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2830700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3020900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2988100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3135800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3163500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3007000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3070700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3222100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3450800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3640300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2933600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1979300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1663600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1313900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>664600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>578900</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3991,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,8 +4022,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3921,71 +4051,72 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>373800</v>
+      </c>
+      <c r="E57" s="3">
         <v>349300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>299300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>298100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>365800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>391600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>342400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>395800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>351200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>298400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>340900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>366000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>494900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>555100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>339400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>209500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>178900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>216100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>121100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>75100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,71 +4126,74 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>206700</v>
+      </c>
+      <c r="E58" s="3">
         <v>199100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>194500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>186000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>162700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>178800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>190600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>191400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>188900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>156000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>150900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>153800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>151000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>176400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>127600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>60500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>51300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>47600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>31800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>15600</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4069,71 +4203,74 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E59" s="3">
         <v>20500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>28700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>49100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>39200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>68900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>81800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>93000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>75400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>80300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>80600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>201100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>275200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>221900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>154100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>93800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>64200</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4143,71 +4280,74 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>677100</v>
+      </c>
+      <c r="E60" s="3">
         <v>651400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>597400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>595600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>640100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>684500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>660000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>714500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>699900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>623600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>648900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>703600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>837800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>935100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>668100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>545300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>452100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>417800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>246700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>154900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4217,71 +4357,74 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1010800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1011500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>991100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1021500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1064800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1105300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1081500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1114700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1118900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>975400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1009900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1002100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1124600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1185400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>797800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>484200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>428000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>578000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>269800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>294500</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4291,8 +4434,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4300,56 +4446,56 @@
         <v>91100</v>
       </c>
       <c r="E62" s="3">
+        <v>91100</v>
+      </c>
+      <c r="F62" s="3">
         <v>92100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>92800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>92700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>92200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>92100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>77100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>72600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>74400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>83300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>75200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>84700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>64100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>117000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>90500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>75400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>71700</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4365,8 +4511,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4439,8 +4588,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4513,8 +4665,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4587,71 +4742,74 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1790800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1765800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1692400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1721100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1812400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1896800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1848500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1906300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1891400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1673400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1742100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1860300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2124700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2184600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4118000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2846300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3073000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1068900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>517500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>450500</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,8 +4819,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4689,8 +4850,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4763,8 +4925,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4837,47 +5002,50 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E70" s="3">
         <v>70200</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>68800</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>67400</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>66100</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>64800</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>63500</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>62300</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>61100</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>58700</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>57500</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -4911,8 +5079,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4985,71 +5156,74 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-776100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-695100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-610200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-466200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-361900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-254700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-235900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-129700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-83300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-15400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-16000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>77500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>110600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>113500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1185900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-868400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1410800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>245000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>147000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>128300</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5059,8 +5233,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5133,8 +5310,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5207,8 +5387,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5281,71 +5464,74 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>542500</v>
+      </c>
+      <c r="E76" s="3">
         <v>617200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>717500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>862000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>875500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>988100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1006900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1101600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1147000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1213600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1211200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1250100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1278800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>119900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-1184400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-867000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-1409400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>244900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>147100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>128300</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5355,8 +5541,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5429,161 +5618,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-79700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-83500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-142600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-100900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-108000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-105000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-45200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-66700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-97900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>22000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>40000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>44000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6600</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>48500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-48500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-31900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-85500</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,82 +5808,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>104700</v>
+      </c>
+      <c r="E83" s="3">
         <v>106000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>77000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>112700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>103400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>112800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>72500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>111500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>108900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>110300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>83600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>69100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>64400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>44600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>90300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>68800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>64100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>44200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>35100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>105600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>36900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>113800</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5758,8 +5960,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5832,8 +6037,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5906,8 +6114,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5980,8 +6191,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6054,82 +6268,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E89" s="3">
         <v>9300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>49500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>900</v>
       </c>
-      <c r="G89" s="3">
-        <v>100400</v>
-      </c>
       <c r="H89" s="3">
+        <v>96700</v>
+      </c>
+      <c r="I89" s="3">
         <v>38700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>76500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>98200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>113500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>79100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>42700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>123600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>153700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>233500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>158500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>172200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>40700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>43700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>37700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>44000</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6156,82 +6376,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-40700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-36600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-34300</v>
       </c>
-      <c r="G91" s="3">
-        <v>-46500</v>
-      </c>
       <c r="H91" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="I91" s="3">
         <v>-52500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-63200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-70000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-61900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-59900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-33100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-52600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-98100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-83200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-116700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-123400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-74600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-41500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-70600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-40500</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6304,8 +6528,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6378,82 +6605,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-30800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-34500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30100</v>
       </c>
-      <c r="G94" s="3">
-        <v>-46200</v>
-      </c>
       <c r="H94" s="3">
+        <v>-42500</v>
+      </c>
+      <c r="I94" s="3">
         <v>-51700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-20500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-67000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-231500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-53300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-28400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-51000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-110600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-525800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-398800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-241400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-53600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-334700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-22900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-55500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-37500</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,8 +6713,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6524,8 +6758,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -6554,8 +6788,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6628,8 +6865,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6702,8 +6942,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6776,82 +7019,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E100" s="3">
         <v>35800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-48900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>61200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-44200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>14200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-66700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-29700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>113700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-22800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-74600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-88000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>327100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>211400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>60200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>57900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>316300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>31300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6894,8 +7143,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6924,78 +7173,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E102" s="3">
         <v>10600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-35100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>32000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-44900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>34800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-28900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>45000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>25300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-10400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
